--- a/Pruebas calificadas/COLEGIO BICENTENARIO DE LA INDEPENDENCIA-302_Ajustado_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO BICENTENARIO DE LA INDEPENDENCIA-302_Ajustado_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1153,11 +1145,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1356,11 +1344,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1559,11 +1543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1758,11 +1738,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -1961,11 +1937,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2156,11 +2128,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2359,11 +2327,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2562,11 +2526,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2765,11 +2725,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -2968,11 +2924,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3171,11 +3123,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3374,11 +3322,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3577,11 +3521,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3780,11 +3720,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -3983,11 +3919,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4186,11 +4118,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4389,11 +4317,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4592,11 +4516,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4795,11 +4715,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -4998,11 +4914,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5197,11 +5109,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5400,11 +5308,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5603,11 +5507,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -5806,11 +5706,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6009,11 +5905,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6212,11 +6104,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6415,11 +6303,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6618,11 +6502,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -6813,11 +6693,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7016,11 +6892,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7219,11 +7091,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7422,11 +7290,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7625,11 +7489,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -7828,11 +7688,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8031,11 +7887,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8234,11 +8086,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8437,11 +8285,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8640,11 +8484,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -8843,11 +8683,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9046,11 +8882,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9249,11 +9081,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9452,11 +9280,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9655,11 +9479,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -9858,11 +9678,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10061,11 +9877,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10264,11 +10076,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10467,11 +10275,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10670,11 +10474,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -10873,11 +10673,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11076,11 +10872,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11279,11 +11071,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11482,11 +11270,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11685,11 +11469,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -11888,11 +11668,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12091,11 +11867,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12294,11 +12066,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12497,11 +12265,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12700,11 +12464,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -12903,11 +12663,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13106,11 +12862,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13309,11 +13061,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13512,11 +13260,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13715,11 +13459,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
@@ -13918,11 +13658,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800457</t>
